--- a/final/IQP_Database (Suha).xlsx
+++ b/final/IQP_Database (Suha).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cshar\OneDrive\Desktop\IT Projects\Christianprojects\sourcesofthequran\final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F999DE-3A4A-475B-83C5-EE9B4F15CBC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0BB820D-4777-4F72-A10F-96EE7F409D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18339,9 +18339,6 @@
     <t>Solomon (Sulaymān)</t>
   </si>
   <si>
-    <t>The Queen of Sheba (Malkaṯ Šəḇā)</t>
-  </si>
-  <si>
     <t>F1: Solomon's Army of Jinn and Birds</t>
   </si>
   <si>
@@ -18573,6 +18570,9 @@
   </si>
   <si>
     <t>F8: Glass Floor Mistaken for Water</t>
+  </si>
+  <si>
+    <t>The Queen of Sheba</t>
   </si>
 </sst>
 </file>
@@ -44122,30 +44122,30 @@
         <v>1410</v>
       </c>
       <c r="E407" s="8" t="s">
+        <v>1446</v>
+      </c>
+      <c r="F407" s="8" t="s">
         <v>1411</v>
       </c>
-      <c r="F407" s="8" t="s">
+      <c r="G407" s="115" t="s">
         <v>1412</v>
       </c>
-      <c r="G407" s="115" t="s">
+      <c r="H407" s="115" t="s">
         <v>1413</v>
-      </c>
-      <c r="H407" s="115" t="s">
-        <v>1414</v>
       </c>
       <c r="P407" s="13" t="s">
         <v>67</v>
       </c>
       <c r="Q407" s="8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="408" spans="1:44" ht="13">
       <c r="A408" s="8" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B408" s="8" t="s">
         <v>1416</v>
-      </c>
-      <c r="B408" s="8" t="s">
-        <v>1417</v>
       </c>
       <c r="C408" s="7">
         <v>46320</v>
@@ -44154,30 +44154,30 @@
         <v>1410</v>
       </c>
       <c r="E408" s="8" t="s">
-        <v>1411</v>
+        <v>1446</v>
       </c>
       <c r="F408" s="8" t="s">
+        <v>1417</v>
+      </c>
+      <c r="G408" s="115" t="s">
         <v>1418</v>
       </c>
-      <c r="G408" s="115" t="s">
-        <v>1419</v>
-      </c>
       <c r="H408" s="115" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="P408" s="13" t="s">
         <v>67</v>
       </c>
       <c r="Q408" s="8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="409" spans="1:44" ht="13">
       <c r="A409" s="8" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B409" s="8" t="s">
         <v>1420</v>
-      </c>
-      <c r="B409" s="8" t="s">
-        <v>1421</v>
       </c>
       <c r="C409" s="7">
         <v>46320</v>
@@ -44186,30 +44186,30 @@
         <v>1410</v>
       </c>
       <c r="E409" s="8" t="s">
-        <v>1411</v>
+        <v>1446</v>
       </c>
       <c r="F409" s="8" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G409" s="115" t="s">
         <v>1422</v>
       </c>
-      <c r="G409" s="115" t="s">
-        <v>1423</v>
-      </c>
       <c r="H409" s="115" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="P409" s="13" t="s">
         <v>67</v>
       </c>
       <c r="Q409" s="8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="410" spans="1:44" ht="13">
       <c r="A410" s="8" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B410" s="8" t="s">
         <v>1424</v>
-      </c>
-      <c r="B410" s="8" t="s">
-        <v>1425</v>
       </c>
       <c r="C410" s="7">
         <v>46320</v>
@@ -44218,30 +44218,30 @@
         <v>1410</v>
       </c>
       <c r="E410" s="8" t="s">
-        <v>1411</v>
+        <v>1446</v>
       </c>
       <c r="F410" s="8" t="s">
+        <v>1425</v>
+      </c>
+      <c r="G410" s="115" t="s">
         <v>1426</v>
       </c>
-      <c r="G410" s="115" t="s">
-        <v>1427</v>
-      </c>
       <c r="H410" s="115" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="P410" s="13" t="s">
         <v>67</v>
       </c>
       <c r="Q410" s="8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="411" spans="1:44" ht="13">
       <c r="A411" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B411" s="8" t="s">
         <v>1428</v>
-      </c>
-      <c r="B411" s="8" t="s">
-        <v>1429</v>
       </c>
       <c r="C411" s="7">
         <v>46320</v>
@@ -44250,30 +44250,30 @@
         <v>1410</v>
       </c>
       <c r="E411" s="8" t="s">
-        <v>1411</v>
+        <v>1446</v>
       </c>
       <c r="F411" s="8" t="s">
+        <v>1429</v>
+      </c>
+      <c r="G411" s="115" t="s">
         <v>1430</v>
       </c>
-      <c r="G411" s="115" t="s">
-        <v>1431</v>
-      </c>
       <c r="H411" s="115" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="P411" s="13" t="s">
         <v>67</v>
       </c>
       <c r="Q411" s="8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="412" spans="1:44" ht="13">
       <c r="A412" s="8" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B412" s="8" t="s">
         <v>1432</v>
-      </c>
-      <c r="B412" s="8" t="s">
-        <v>1433</v>
       </c>
       <c r="C412" s="7">
         <v>46320</v>
@@ -44282,30 +44282,30 @@
         <v>1410</v>
       </c>
       <c r="E412" s="8" t="s">
-        <v>1411</v>
+        <v>1446</v>
       </c>
       <c r="F412" s="8" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G412" s="115" t="s">
         <v>1434</v>
       </c>
-      <c r="G412" s="115" t="s">
-        <v>1435</v>
-      </c>
       <c r="H412" s="115" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="P412" s="13" t="s">
         <v>67</v>
       </c>
       <c r="Q412" s="8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="413" spans="1:44" ht="13">
       <c r="A413" s="8" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B413" s="8" t="s">
         <v>1436</v>
-      </c>
-      <c r="B413" s="8" t="s">
-        <v>1437</v>
       </c>
       <c r="C413" s="7">
         <v>46320</v>
@@ -44314,30 +44314,30 @@
         <v>1410</v>
       </c>
       <c r="E413" s="8" t="s">
-        <v>1411</v>
+        <v>1446</v>
       </c>
       <c r="F413" s="8" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="G413" s="115" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H413" s="115" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="P413" s="13" t="s">
         <v>67</v>
       </c>
       <c r="Q413" s="8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="414" spans="1:44" ht="13">
       <c r="A414" s="8" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B414" s="8" t="s">
         <v>1439</v>
-      </c>
-      <c r="B414" s="8" t="s">
-        <v>1440</v>
       </c>
       <c r="C414" s="7">
         <v>46320</v>
@@ -44346,30 +44346,30 @@
         <v>1410</v>
       </c>
       <c r="E414" s="8" t="s">
-        <v>1411</v>
+        <v>1446</v>
       </c>
       <c r="F414" s="8" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="G414" s="115" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H414" s="115" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="P414" s="13" t="s">
         <v>67</v>
       </c>
       <c r="Q414" s="8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="415" spans="1:44" ht="13">
       <c r="A415" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B415" s="8" t="s">
         <v>1442</v>
-      </c>
-      <c r="B415" s="8" t="s">
-        <v>1443</v>
       </c>
       <c r="C415" s="7">
         <v>46320</v>
@@ -44378,22 +44378,22 @@
         <v>1410</v>
       </c>
       <c r="E415" s="8" t="s">
-        <v>1411</v>
+        <v>1446</v>
       </c>
       <c r="F415" s="8" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="G415" s="115" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H415" s="115" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="P415" s="13" t="s">
         <v>67</v>
       </c>
       <c r="Q415" s="8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="416" spans="1:44" ht="12.5">
